--- a/intern_schedule_2026-2027/schedules/TYP_October_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_October_2026.xlsx
@@ -517,17 +517,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -542,17 +542,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BUTT</t>
+          <t>MACNEILLE S, BUTT A</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -567,13 +567,13 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BUTT  (24H)</t>
+          <t>BUTT A  (24H)</t>
         </is>
       </c>
     </row>
@@ -588,13 +588,13 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -609,17 +609,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>BUTT, AHLUWALIA</t>
+          <t>BUTT A, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, AHLUWALIA</t>
+          <t>BRONSON I, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, BUTT</t>
+          <t>BRONSON I, BUTT A</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>BUTT, AHLUWALIA</t>
+          <t>BUTT A, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -734,13 +734,13 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA  (24H)</t>
+          <t>AHLUWALIA Sr  (24H)</t>
         </is>
       </c>
     </row>
@@ -755,13 +755,13 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>BUTT</t>
+          <t>BUTT A</t>
         </is>
       </c>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>MULLINS, AHLUWALIA</t>
+          <t>MULLINS H, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -801,17 +801,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, AHLUWALIA</t>
+          <t>MACNEILLE S, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, MULLINS</t>
+          <t>MACNEILLE S, MULLINS H</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -851,17 +851,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, MULLINS</t>
+          <t>MACNEILLE S, MULLINS H</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -901,13 +901,13 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE  (24H)</t>
+          <t>MACNEILLE S  (24H)</t>
         </is>
       </c>
     </row>
@@ -922,13 +922,13 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, CHIASSON</t>
+          <t>MACNEILLE S, CHIASSON M</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -968,17 +968,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, CHIASSON</t>
+          <t>BRONSON I, CHIASSON M</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -1043,17 +1043,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
     </row>
@@ -1068,13 +1068,13 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>BRONSON I  (24H)</t>
         </is>
       </c>
     </row>
@@ -1089,13 +1089,13 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>BRONSON, MULLINS</t>
+          <t>BRONSON I, MULLINS H</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1135,17 +1135,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, MULLINS</t>
+          <t>MACNEILLE S, MULLINS H</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>MACNEILLE S, BRONSON I</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1185,17 +1185,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>MACNEILLE S</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1210,17 +1210,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>MACNEILLE, MULLINS</t>
+          <t>MACNEILLE S, MULLINS H</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>CHIASSON M</t>
         </is>
       </c>
     </row>
@@ -1235,13 +1235,13 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>MULLINS H</t>
         </is>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>MULLINS  (24H)</t>
+          <t>MULLINS H  (24H)</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_October_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_October_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <i val="1"/>
@@ -78,23 +79,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,19 +519,19 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -540,61 +544,61 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BUTT A</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
         </is>
       </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, BRONSON</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>BUTT A  (24H)</t>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -607,19 +611,19 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, BUTT</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -632,19 +636,19 @@
       <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BUTT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -657,19 +661,19 @@
       <c r="B9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BRONSON</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, BUTT A</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
         </is>
       </c>
     </row>
@@ -682,19 +686,19 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -707,61 +711,61 @@
       <c r="B11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>BUTT A, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, BUTT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr  (24H)</t>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>BUTT</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>BUTT  (24H)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>BUTT A</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -774,19 +778,19 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -799,19 +803,19 @@
       <c r="B15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -824,19 +828,19 @@
       <c r="B16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr, MULLINS</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -849,19 +853,19 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -874,61 +878,61 @@
       <c r="B18" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>MACNEILLE  (24H)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>AHLUWALIA Sr</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE S  (24H)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -941,19 +945,19 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -966,19 +970,19 @@
       <c r="B22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -991,19 +995,19 @@
       <c r="B23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1020,19 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
@@ -1041,61 +1045,61 @@
       <c r="B25" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON I  (24H)</t>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>CHIASSON  (24H)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1108,19 +1112,19 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON, BRONSON</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1133,19 +1137,19 @@
       <c r="B29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, BRONSON</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1162,19 @@
       <c r="B30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1183,19 +1187,19 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -1208,57 +1212,57 @@
       <c r="B32" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>MACNEILLE S, MULLINS H</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>CHIASSON M</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, BRONSON</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS H</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS H  (24H)</t>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -1289,7 +1293,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -1320,7 +1324,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -1351,7 +1355,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -1382,7 +1386,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>

--- a/intern_schedule_2026-2027/schedules/TYP_October_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_October_2026.xlsx
@@ -526,12 +526,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -905,13 +905,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE  (24H)</t>
+          <t>AHLUWALIA Sr  (24H)</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>CHIASSON</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, CHIASSON</t>
+          <t>MACNEILLE, BRONSON</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">

--- a/intern_schedule_2026-2027/schedules/TYP_October_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_October_2026.xlsx
@@ -526,12 +526,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>BUTT, BRONSON</t>
+          <t>BUTT, MACNEILLE</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>MACNEILLE  (24H)</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, BUTT</t>
+          <t>MACNEILLE, BUTT</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BUTT</t>
+          <t>BRONSON, BUTT</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>BRONSON, MACNEILLE</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BUTT</t>
+          <t>BRONSON, BUTT</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -759,13 +759,13 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>MULLINS, MACNEILLE</t>
+          <t>MULLINS, BRONSON</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr, MACNEILLE</t>
+          <t>AHLUWALIA Sr, BRONSON</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr, MACNEILLE</t>
+          <t>AHLUWALIA Sr, BRONSON</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -905,13 +905,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr  (24H)</t>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>BRONSON, CHIASSON</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, CHIASSON</t>
+          <t>MACNEILLE, CHIASSON</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, MACNEILLE</t>
+          <t>MACNEILLE, BRONSON</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, CHIASSON</t>
+          <t>MACNEILLE, CHIASSON</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1093,13 +1093,13 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, BRONSON</t>
+          <t>CHIASSON, MACNEILLE</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>MULLINS, BRONSON</t>
+          <t>MULLINS, MACNEILLE</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>MULLINS, BRONSON</t>
+          <t>MULLINS, MACNEILLE</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1239,13 +1239,13 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>MACNEILLE  (24H)</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stephen MacNeille</t>
+          <t>Isaac Bronson</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>Isaac Bronson</t>
+          <t>Stephen MacNeille</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
